--- a/data/MK_YFINANCE_DATA_20260609.xlsx
+++ b/data/MK_YFINANCE_DATA_20260609.xlsx
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>8052.1299</v>
+        <v>8067.75</v>
       </c>
     </row>
     <row r="182">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>979.96</v>
+        <v>966.36</v>
       </c>
     </row>
     <row r="206">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1283.9</v>
+        <v>1288.17</v>
       </c>
     </row>
     <row r="230">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>17575</v>
+        <v>17170</v>
       </c>
     </row>
     <row r="253">

--- a/data/MK_YFINANCE_DATA_20260609.xlsx
+++ b/data/MK_YFINANCE_DATA_20260609.xlsx
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>8067.75</v>
+        <v>8107.8799</v>
       </c>
     </row>
     <row r="182">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>966.36</v>
+        <v>968.37</v>
       </c>
     </row>
     <row r="206">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1288.17</v>
+        <v>1294.88</v>
       </c>
     </row>
     <row r="230">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>17170</v>
+        <v>17155</v>
       </c>
     </row>
     <row r="253">
